--- a/33張test裁切結果.xlsx
+++ b/33張test裁切結果.xlsx
@@ -456,14 +456,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001_jpg.rf.ee9354a1be0a727b6de69c334f6c0290.jpg</t>
+          <t>001_jpg.rf.26d64b4af7fce706bb3cba9a94640a2f.jpg</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.785</v>
+        <v>0.855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -472,12 +472,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\001_jpg.rf.ee9354a1be0a727b6de69c334f6c0290.jpg</t>
+          <t>cropped_test_teeth\001_jpg.rf.26d64b4af7fce706bb3cba9a94640a2f.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>165,2,281,327</t>
+          <t>179,38,269,290</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -489,14 +489,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002_jpg.rf.01bab112ee25de61c27df7796ed9bda7.jpg</t>
+          <t>002_jpg.rf.ebe8c919bbe79621de3f9d2c2ed05e36.jpg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.826</v>
+        <v>0.895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -505,12 +505,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\002_jpg.rf.01bab112ee25de61c27df7796ed9bda7.jpg</t>
+          <t>cropped_test_teeth\002_jpg.rf.ebe8c919bbe79621de3f9d2c2ed05e36.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46,104,199,400</t>
+          <t>62,143,174,394</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -522,14 +522,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003_jpg.rf.d4c40b50e95959169d93b17f0bbf447b.jpg</t>
+          <t>003_jpg.rf.b1908a93192d25dce501afeee21c128c.jpg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.888</v>
+        <v>0.894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -538,12 +538,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\003_jpg.rf.d4c40b50e95959169d93b17f0bbf447b.jpg</t>
+          <t>cropped_test_teeth\003_jpg.rf.b1908a93192d25dce501afeee21c128c.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115,27,253,400</t>
+          <t>131,73,238,388</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -555,14 +555,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004_jpg.rf.29e120c50af9ccb103020a4a198b8296.jpg</t>
+          <t>004_jpg.rf.eff436d43ff0e4e14f3cf98402412e4c.jpg</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.789</v>
+        <v>0.879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\004_jpg.rf.29e120c50af9ccb103020a4a198b8296.jpg</t>
+          <t>cropped_test_teeth\004_jpg.rf.eff436d43ff0e4e14f3cf98402412e4c.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>194,94,295,400</t>
+          <t>204,130,285,374</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -588,14 +588,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005_jpg.rf.5203d9b642e85b9fcf0a30ea1cc32e41.jpg</t>
+          <t>005_jpg.rf.fd9c0ce3b040241497d9dc772869dbc0.jpg</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.793</v>
+        <v>0.922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -604,12 +604,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\005_jpg.rf.5203d9b642e85b9fcf0a30ea1cc32e41.jpg</t>
+          <t>cropped_test_teeth\005_jpg.rf.fd9c0ce3b040241497d9dc772869dbc0.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>116,73,249,400</t>
+          <t>131,107,231,372</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -621,14 +621,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006_jpg.rf.bd3df0e76e04fa0d48cd9a62a35f7b3a.jpg</t>
+          <t>006_jpg.rf.23739e22d7c1ac7e038d6c1b63727b1b.jpg</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.793</v>
+        <v>0.875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -637,31 +637,31 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\006_jpg.rf.bd3df0e76e04fa0d48cd9a62a35f7b3a.jpg</t>
+          <t>cropped_test_teeth\006_jpg.rf.23739e22d7c1ac7e038d6c1b63727b1b.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>128,34,285,400</t>
+          <t>154,83,266,368</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>007_jpg.rf.1ec5ad7f4af32b2d51e394416510da00.jpg</t>
+          <t>007_jpg.rf.e90d85fcab8873bcc0c04824d0fd697a.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.825</v>
+        <v>0.925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -670,12 +670,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\007_jpg.rf.1ec5ad7f4af32b2d51e394416510da00.jpg</t>
+          <t>cropped_test_teeth\007_jpg.rf.e90d85fcab8873bcc0c04824d0fd697a.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>96,13,241,400</t>
+          <t>119,56,223,368</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -687,14 +687,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>008_jpg.rf.f6c21a1626ee1016a5abced7d053e319.jpg</t>
+          <t>008_jpg.rf.a26cfdf2a008c9a3efb1c3741b326600.jpg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.866</v>
+        <v>0.824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\008_jpg.rf.f6c21a1626ee1016a5abced7d053e319.jpg</t>
+          <t>cropped_test_teeth\008_jpg.rf.a26cfdf2a008c9a3efb1c3741b326600.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>147,70,244,375</t>
+          <t>147,98,232,342</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -720,14 +720,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>009_jpg.rf.f158409927e8971fac5e5fdbbfe2cf4b.jpg</t>
+          <t>009_jpg.rf.4df579de97813a043f771194b49e1a04.jpg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.786</v>
+        <v>0.838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -736,12 +736,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\009_jpg.rf.f158409927e8971fac5e5fdbbfe2cf4b.jpg</t>
+          <t>cropped_test_teeth\009_jpg.rf.4df579de97813a043f771194b49e1a04.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>151,88,282,400</t>
+          <t>165,126,263,398</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -753,14 +753,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>010_jpg.rf.4d1eb586c7226392d9b5ea9178657cf9.jpg</t>
+          <t>010_jpg.rf.ec9d384ce8506ef686d26435bd5262e7.jpg</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -769,12 +769,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\010_jpg.rf.4d1eb586c7226392d9b5ea9178657cf9.jpg</t>
+          <t>cropped_test_teeth\010_jpg.rf.ec9d384ce8506ef686d26435bd5262e7.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>85,51,173,302</t>
+          <t>94,81,167,275</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -786,14 +786,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011_jpg.rf.977178851bffcc760d22679bc467d2ef.jpg</t>
+          <t>011_jpg.rf.188e8c8bdf31b26620d6221f09fd444a.jpg</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.921</v>
+        <v>0.948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -802,31 +802,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\011_jpg.rf.977178851bffcc760d22679bc467d2ef.jpg</t>
+          <t>cropped_test_teeth\011_jpg.rf.188e8c8bdf31b26620d6221f09fd444a.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>121,36,267,400</t>
+          <t>137,81,250,385</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012_jpg.rf.23c24aa9d7984fab5c7293a83ff96b98.jpg</t>
+          <t>012_jpg.rf.95a4280570f81e990b0672e137123f00.jpg</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.865</v>
+        <v>0.915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\012_jpg.rf.23c24aa9d7984fab5c7293a83ff96b98.jpg</t>
+          <t>cropped_test_teeth\012_jpg.rf.95a4280570f81e990b0672e137123f00.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>202,47,340,400</t>
+          <t>220,88,325,358</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -852,14 +852,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>013_jpg.rf.90e3b77a95b8ab0950b18aeb60a43f48.jpg</t>
+          <t>013_jpg.rf.4c019428deb9ebda1a1031e06cf21b2d.jpg</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.874</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -868,31 +868,31 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\013_jpg.rf.90e3b77a95b8ab0950b18aeb60a43f48.jpg</t>
+          <t>cropped_test_teeth\013_jpg.rf.4c019428deb9ebda1a1031e06cf21b2d.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>106,49,240,400</t>
+          <t>126,94,223,371</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>014_jpg.rf.8b60637634bd9582c5402b9b3e9aa2c3.jpg</t>
+          <t>014_jpg.rf.3c16ab39680acc322316a655dbc99196.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.887</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\014_jpg.rf.8b60637634bd9582c5402b9b3e9aa2c3.jpg</t>
+          <t>cropped_test_teeth\014_jpg.rf.3c16ab39680acc322316a655dbc99196.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>140,0,240,287</t>
+          <t>148,4,233,253</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -918,14 +918,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015_jpg.rf.cdb2947c5f5eaa955ff9c4b111aeaadd.jpg</t>
+          <t>015_jpg.rf.73e9cf853e7b9c5474c463eab089c876.jpg</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.835</v>
+        <v>0.963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\015_jpg.rf.cdb2947c5f5eaa955ff9c4b111aeaadd.jpg</t>
+          <t>cropped_test_teeth\015_jpg.rf.73e9cf853e7b9c5474c463eab089c876.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>153,2,248,336</t>
+          <t>164,38,233,295</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -951,14 +951,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>016_jpg.rf.52aab9e8bcc30ec8879c21d4ab0f3724.jpg</t>
+          <t>016_jpg.rf.e4c9d7dfdf9ddac85121698887e3fcf9.jpg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.839</v>
+        <v>0.877</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\016_jpg.rf.52aab9e8bcc30ec8879c21d4ab0f3724.jpg</t>
+          <t>cropped_test_teeth\016_jpg.rf.e4c9d7dfdf9ddac85121698887e3fcf9.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>172,44,254,338</t>
+          <t>181,75,245,307</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -984,14 +984,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>017_jpg.rf.4f8a3e32e6ca4da5212b29c28e23a692.jpg</t>
+          <t>017_jpg.rf.bcc03bba4330d37600812dfd900a6c98.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.889</v>
+        <v>0.911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\017_jpg.rf.4f8a3e32e6ca4da5212b29c28e23a692.jpg</t>
+          <t>cropped_test_teeth\017_jpg.rf.bcc03bba4330d37600812dfd900a6c98.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>81,31,202,400</t>
+          <t>90,73,198,379</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1017,14 +1017,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>018_jpg.rf.0645a264fd1ed86ce4fc698cc94654a2.jpg</t>
+          <t>018_jpg.rf.3f56a35aa4805306df0598026f7f051c.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\018_jpg.rf.0645a264fd1ed86ce4fc698cc94654a2.jpg</t>
+          <t>cropped_test_teeth\018_jpg.rf.3f56a35aa4805306df0598026f7f051c.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>140,70,277,400</t>
+          <t>160,113,258,391</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1050,14 +1050,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>019_jpg.rf.78370325a20d04e2041981a94352f2f3.jpg</t>
+          <t>019_jpg.rf.52864781a13f7fbec6eb66084ed5823f.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.903</v>
+        <v>0.95</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\019_jpg.rf.78370325a20d04e2041981a94352f2f3.jpg</t>
+          <t>cropped_test_teeth\019_jpg.rf.52864781a13f7fbec6eb66084ed5823f.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>180,28,317,400</t>
+          <t>196,75,298,392</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1083,14 +1083,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>020_jpg.rf.96b92c670dffd928c5f5218cfbd6c643.jpg</t>
+          <t>020_jpg.rf.74f065d79dba86d09007843d47da9c23.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.822</v>
+        <v>0.922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\020_jpg.rf.96b92c670dffd928c5f5218cfbd6c643.jpg</t>
+          <t>cropped_test_teeth\020_jpg.rf.74f065d79dba86d09007843d47da9c23.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>90,124,214,400</t>
+          <t>106,155,198,373</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1116,14 +1116,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>021_jpg.rf.b6187e94964f263a6d87859c1b6a7658.jpg</t>
+          <t>021_jpg.rf.daa2d35e1c7445885774120f9a2ba2e5.jpg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.781</v>
+        <v>0.956</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\021_jpg.rf.b6187e94964f263a6d87859c1b6a7658.jpg</t>
+          <t>cropped_test_teeth\021_jpg.rf.daa2d35e1c7445885774120f9a2ba2e5.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>138,99,275,400</t>
+          <t>161,138,252,397</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1149,14 +1149,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>022_jpg.rf.23c64f8b776f3c882db3f481c8cba337.jpg</t>
+          <t>022_jpg.rf.54cf361b4e43c6fe903fc4eb1919efb2.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.898</v>
+        <v>0.899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1165,31 +1165,31 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\022_jpg.rf.23c64f8b776f3c882db3f481c8cba337.jpg</t>
+          <t>cropped_test_teeth\022_jpg.rf.54cf361b4e43c6fe903fc4eb1919efb2.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>89,75,219,400</t>
+          <t>109,116,203,392</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>023_jpg.rf.d93085fb44fe63f8b003210e9f9f8c59.jpg</t>
+          <t>023_jpg.rf.66a29ce1f79ebb86d1bed49ace6963fd.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.851</v>
+        <v>0.956</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\023_jpg.rf.d93085fb44fe63f8b003210e9f9f8c59.jpg</t>
+          <t>cropped_test_teeth\023_jpg.rf.66a29ce1f79ebb86d1bed49ace6963fd.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>107,106,261,400</t>
+          <t>126,143,237,386</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1215,14 +1215,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>024_jpg.rf.39a32d096d830b191b165653a7d0c5c5.jpg</t>
+          <t>024_jpg.rf.e9ebc38820f6d84a159be64810cf2b42.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.778</v>
+        <v>0.964</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\024_jpg.rf.39a32d096d830b191b165653a7d0c5c5.jpg</t>
+          <t>cropped_test_teeth\024_jpg.rf.e9ebc38820f6d84a159be64810cf2b42.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>205,90,345,400</t>
+          <t>226,126,321,365</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1248,28 +1248,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>025_jpg.rf.9848f1ef31c409510807dbceb3f6a784.jpg</t>
+          <t>025_jpg.rf.1d61d795674a24234f5f6c228dda505b.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>0.197</v>
+        <v>0.911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>⚠️ 最佳IoU只有0.197(&lt;0.3)，配對不可靠，退回用舊標註bbox裁切</t>
+          <t>✅ 配對成功，使用偵測器框裁切</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\025_jpg.rf.9848f1ef31c409510807dbceb3f6a784.jpg</t>
+          <t>cropped_test_teeth\025_jpg.rf.1d61d795674a24234f5f6c228dda505b.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>63,31,208,370</t>
+          <t>84,82,186,336</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1281,14 +1281,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>026_jpg.rf.4cf64dbe631bbb599b3882b8d8e4cb99.jpg</t>
+          <t>026_jpg.rf.d135b38b12794acb3a0dd131078184fe.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.795</v>
+        <v>0.907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\026_jpg.rf.4cf64dbe631bbb599b3882b8d8e4cb99.jpg</t>
+          <t>cropped_test_teeth\026_jpg.rf.d135b38b12794acb3a0dd131078184fe.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>146,27,317,400</t>
+          <t>171,73,287,356</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1314,14 +1314,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>027_jpg.rf.a05b7156d6865ff7b71e44cec95c691f.jpg</t>
+          <t>027_jpg.rf.9be636888e7c341c8c41e6a2766ce5fa.jpg</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.822</v>
+        <v>0.899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\027_jpg.rf.a05b7156d6865ff7b71e44cec95c691f.jpg</t>
+          <t>cropped_test_teeth\027_jpg.rf.9be636888e7c341c8c41e6a2766ce5fa.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>84,78,218,400</t>
+          <t>110,108,202,371</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1347,14 +1347,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>028_jpg.rf.f7107f568c4ad6c617b093bf1cf338e4.jpg</t>
+          <t>028_jpg.rf.95ad6712c1dbf3ad22b5803b15393683.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.805</v>
+        <v>0.921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\028_jpg.rf.f7107f568c4ad6c617b093bf1cf338e4.jpg</t>
+          <t>cropped_test_teeth\028_jpg.rf.95ad6712c1dbf3ad22b5803b15393683.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>172,75,318,400</t>
+          <t>192,117,298,400</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1380,14 +1380,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>029_jpg.rf.544305f8e87d1b6621256f4c2bd7e259.jpg</t>
+          <t>029_jpg.rf.8c2f541015d35e53e936b01eadb34e47.jpg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.858</v>
+        <v>0.91</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\029_jpg.rf.544305f8e87d1b6621256f4c2bd7e259.jpg</t>
+          <t>cropped_test_teeth\029_jpg.rf.8c2f541015d35e53e936b01eadb34e47.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102,114,216,396</t>
+          <t>114,143,206,366</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1413,14 +1413,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>030_jpg.rf.483902b24d18eca035256d4a36d06510.jpg</t>
+          <t>030_jpg.rf.0b36a69f48929ab107a690f010f047a6.jpg</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.898</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\030_jpg.rf.483902b24d18eca035256d4a36d06510.jpg</t>
+          <t>cropped_test_teeth\030_jpg.rf.0b36a69f48929ab107a690f010f047a6.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>133,36,280,400</t>
+          <t>150,76,263,361</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1446,14 +1446,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>031_jpg.rf.925e9bfa9ad7afcc7ec37b2d940763d7.jpg</t>
+          <t>031_jpg.rf.f392beb3fe244231d59337504e095a11.jpg</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\031_jpg.rf.925e9bfa9ad7afcc7ec37b2d940763d7.jpg</t>
+          <t>cropped_test_teeth\031_jpg.rf.f392beb3fe244231d59337504e095a11.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>168,82,311,400</t>
+          <t>187,118,292,400</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1479,14 +1479,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>032_jpg.rf.5c7714f7178b74d6a97740e6ce207e7d.jpg</t>
+          <t>032_jpg.rf.a1483732b3cfe35413834e422f2e1c8f.jpg</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>0.865</v>
+        <v>0.93</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\032_jpg.rf.5c7714f7178b74d6a97740e6ce207e7d.jpg</t>
+          <t>cropped_test_teeth\032_jpg.rf.a1483732b3cfe35413834e422f2e1c8f.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>78,89,202,400</t>
+          <t>88,126,192,400</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1512,14 +1512,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>033_jpg.rf.0415354c612353b21bccc7201b829396.jpg</t>
+          <t>033_jpg.rf.4e99d92e4c1804a1a445d3da4dd329bc.jpg</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.909</v>
+        <v>0.921</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cropped_test_teeth\033_jpg.rf.0415354c612353b21bccc7201b829396.jpg</t>
+          <t>cropped_test_teeth\033_jpg.rf.4e99d92e4c1804a1a445d3da4dd329bc.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>135,56,273,400</t>
+          <t>148,98,258,375</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
